--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation-subordonnee.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation-subordonnee.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:34:08+00:00</t>
+    <t>2026-04-15T07:49:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation-subordonnee.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation-subordonnee.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:49:49+00:00</t>
+    <t>2026-04-16T07:52:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation-subordonnee.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation-subordonnee.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation-subordonnee.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation-subordonnee.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation-subordonnee.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation-subordonnee.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation-subordonnee.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation-subordonnee.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation-subordonnee.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation-subordonnee.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation-subordonnee.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation-subordonnee.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$134</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3832" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4181" uniqueCount="424">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -523,6 +523,132 @@
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-sop-class-cisis</t>
   </si>
   <si>
+    <t>Observation.code.nullFlavor</t>
+  </si>
+  <si>
+    <t>Observation.code.code</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
+</t>
+  </si>
+  <si>
+    <t>The text or phrase used as the basis for the coding.</t>
+  </si>
+  <si>
+    <t>CD.originalText</t>
+  </si>
+  <si>
+    <t>Observation.code.qualifier</t>
+  </si>
+  <si>
+    <t>Qualifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
+</t>
+  </si>
+  <si>
+    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
+  </si>
+  <si>
+    <t>CD.qualifier</t>
+  </si>
+  <si>
+    <t>Observation.code.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
+  </si>
+  <si>
     <t>Observation.derivationExpr</t>
   </si>
   <si>
@@ -531,10 +657,6 @@
   </si>
   <si>
     <t>Observation.text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
-</t>
   </si>
   <si>
     <t>Partie narrative de l'observation</t>
@@ -1528,7 +1650,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK123"/>
+  <dimension ref="A1:AK134"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="75.828125" customWidth="true" bestFit="true"/>
@@ -4229,7 +4351,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>157</v>
       </c>
@@ -4248,7 +4370,7 @@
         <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>74</v>
@@ -4543,7 +4665,9 @@
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E30" s="2"/>
+      <c r="E30" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
@@ -4560,10 +4684,12 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>166</v>
+        <v>85</v>
       </c>
       <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
+      <c r="M30" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4589,13 +4715,11 @@
         <v>74</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>74</v>
@@ -4613,7 +4737,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>165</v>
+        <v>89</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4633,18 +4757,20 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E31" s="2"/>
+      <c r="E31" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>75</v>
@@ -4659,13 +4785,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4716,7 +4840,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4734,28 +4858,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>74</v>
@@ -4764,11 +4888,11 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>86</v>
+        <v>171</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4795,11 +4919,13 @@
         <v>74</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y32" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z32" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>74</v>
@@ -4817,7 +4943,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>89</v>
+        <v>172</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4837,17 +4963,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
@@ -4865,11 +4991,11 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4896,11 +5022,13 @@
         <v>74</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y33" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z33" t="s" s="2">
-        <v>174</v>
+        <v>74</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>74</v>
@@ -4918,7 +5046,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4938,17 +5066,17 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>80</v>
@@ -4966,7 +5094,7 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>178</v>
+        <v>102</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
@@ -5039,7 +5167,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>181</v>
       </c>
@@ -5060,7 +5188,7 @@
         <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>74</v>
@@ -5069,7 +5197,7 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
@@ -5100,29 +5228,31 @@
         <v>74</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5142,18 +5272,16 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E36" t="s" s="2">
-        <v>187</v>
-      </c>
+      <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
@@ -5170,11 +5298,11 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>85</v>
+        <v>186</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5225,7 +5353,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5245,20 +5373,18 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E37" t="s" s="2">
-        <v>191</v>
-      </c>
+      <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>75</v>
@@ -5273,11 +5399,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5289,7 +5415,7 @@
         <v>74</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>193</v>
+        <v>74</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>74</v>
@@ -5304,11 +5430,13 @@
         <v>74</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="Y37" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z37" t="s" s="2">
-        <v>195</v>
+        <v>74</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>74</v>
@@ -5326,7 +5454,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5346,16 +5474,18 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E38" s="2"/>
+      <c r="E38" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
@@ -5372,10 +5502,12 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
+      <c r="M38" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5401,11 +5533,13 @@
         <v>74</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>198</v>
+        <v>74</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>74</v>
@@ -5423,7 +5557,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5443,21 +5577,23 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E39" s="2"/>
+      <c r="E39" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>74</v>
@@ -5469,17 +5605,13 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>203</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>74</v>
@@ -5528,13 +5660,13 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>74</v>
@@ -5548,23 +5680,23 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F40" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>74</v>
@@ -5576,13 +5708,11 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5633,13 +5763,13 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>74</v>
@@ -5653,18 +5783,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E41" t="s" s="2">
-        <v>211</v>
-      </c>
+      <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
@@ -5681,12 +5809,10 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>168</v>
+        <v>207</v>
       </c>
       <c r="L41" s="2"/>
-      <c r="M41" t="s" s="2">
-        <v>212</v>
-      </c>
+      <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5736,7 +5862,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5754,12 +5880,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5773,7 +5899,7 @@
         <v>75</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>74</v>
@@ -5782,10 +5908,14 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5811,11 +5941,13 @@
         <v>74</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y42" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z42" t="s" s="2">
-        <v>215</v>
+        <v>74</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>74</v>
@@ -5833,7 +5965,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5851,18 +5983,20 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E43" s="2"/>
+      <c r="E43" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
@@ -5870,7 +6004,7 @@
         <v>75</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>74</v>
@@ -5879,13 +6013,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>218</v>
+        <v>86</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5912,13 +6044,11 @@
         <v>74</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>74</v>
@@ -5936,7 +6066,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>216</v>
+        <v>89</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5956,16 +6086,18 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E44" s="2"/>
+      <c r="E44" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
@@ -5982,10 +6114,12 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>220</v>
+        <v>85</v>
       </c>
       <c r="L44" s="2"/>
-      <c r="M44" s="2"/>
+      <c r="M44" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6011,11 +6145,11 @@
         <v>74</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>194</v>
+        <v>87</v>
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>74</v>
@@ -6033,7 +6167,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6053,16 +6187,18 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E45" s="2"/>
+      <c r="E45" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
@@ -6079,10 +6215,12 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
+      <c r="M45" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6132,7 +6270,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6152,16 +6290,18 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E46" s="2"/>
+      <c r="E46" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
@@ -6178,10 +6318,12 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
+      <c r="M46" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6211,25 +6353,25 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF46" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6258,12 +6400,14 @@
       <c r="D47" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E47" s="2"/>
+      <c r="E47" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>74</v>
@@ -6275,10 +6419,12 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>227</v>
+        <v>85</v>
       </c>
       <c r="L47" s="2"/>
-      <c r="M47" s="2"/>
+      <c r="M47" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6328,13 +6474,13 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>74</v>
@@ -6348,21 +6494,23 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E48" s="2"/>
+      <c r="E48" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>74</v>
@@ -6374,10 +6522,12 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>220</v>
+        <v>85</v>
       </c>
       <c r="L48" s="2"/>
-      <c r="M48" s="2"/>
+      <c r="M48" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6388,7 +6538,7 @@
         <v>74</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>74</v>
+        <v>233</v>
       </c>
       <c r="T48" t="s" s="2">
         <v>74</v>
@@ -6403,11 +6553,11 @@
         <v>74</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>87</v>
+        <v>234</v>
       </c>
       <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>74</v>
@@ -6425,13 +6575,13 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>74</v>
@@ -6445,10 +6595,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6459,7 +6609,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>74</v>
@@ -6471,7 +6621,7 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>220</v>
+        <v>85</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
@@ -6500,11 +6650,11 @@
         <v>74</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>194</v>
+        <v>87</v>
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>74</v>
@@ -6522,13 +6672,13 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>74</v>
@@ -6542,10 +6692,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6556,7 +6706,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>74</v>
@@ -6568,13 +6718,17 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="L50" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="M50" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>74</v>
@@ -6623,13 +6777,13 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>74</v>
@@ -6643,18 +6797,20 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E51" s="2"/>
+      <c r="E51" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>75</v>
@@ -6669,10 +6825,14 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="L51" s="2"/>
-      <c r="M51" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -6722,7 +6882,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6742,21 +6902,23 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E52" s="2"/>
+      <c r="E52" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>74</v>
@@ -6768,10 +6930,12 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>237</v>
+        <v>194</v>
       </c>
       <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
+      <c r="M52" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -6821,13 +6985,13 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>74</v>
@@ -6841,10 +7005,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6855,7 +7019,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>74</v>
@@ -6867,7 +7031,7 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>239</v>
+        <v>91</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -6896,13 +7060,11 @@
         <v>74</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>74</v>
+        <v>255</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>74</v>
@@ -6920,13 +7082,13 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>74</v>
@@ -6938,12 +7100,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6954,10 +7116,10 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>74</v>
@@ -6966,10 +7128,14 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="L54" s="2"/>
-      <c r="M54" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7019,13 +7185,13 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>74</v>
@@ -7039,10 +7205,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7053,7 +7219,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>74</v>
@@ -7065,7 +7231,7 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -7094,13 +7260,11 @@
         <v>74</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>74</v>
+        <v>261</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>74</v>
@@ -7118,13 +7282,13 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>74</v>
@@ -7138,10 +7302,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7152,7 +7316,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>74</v>
@@ -7164,7 +7328,7 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -7217,13 +7381,13 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>74</v>
@@ -7237,10 +7401,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7251,10 +7415,10 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>74</v>
@@ -7263,7 +7427,7 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>247</v>
+        <v>91</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -7292,35 +7456,35 @@
         <v>74</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>74</v>
+        <v>265</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AC57" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AD57" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>74</v>
@@ -7334,14 +7498,12 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>74</v>
       </c>
@@ -7350,7 +7512,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>74</v>
@@ -7362,11 +7524,9 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="L58" s="2"/>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7417,7 +7577,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7437,23 +7597,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E59" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>74</v>
@@ -7465,12 +7623,10 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>85</v>
+        <v>260</v>
       </c>
       <c r="L59" s="2"/>
-      <c r="M59" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M59" s="2"/>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -7500,7 +7656,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>88</v>
+        <v>269</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7518,13 +7674,13 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>89</v>
+        <v>268</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>74</v>
@@ -7538,10 +7694,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7564,12 +7720,10 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>91</v>
+        <v>260</v>
       </c>
       <c r="L60" s="2"/>
-      <c r="M60" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M60" s="2"/>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -7595,13 +7749,11 @@
         <v>74</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>74</v>
+        <v>271</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>74</v>
@@ -7619,7 +7771,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>93</v>
+        <v>270</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7639,10 +7791,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7653,7 +7805,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>74</v>
@@ -7665,11 +7817,11 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" t="s" s="2">
-        <v>96</v>
+        <v>273</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7720,19 +7872,19 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>74</v>
@@ -7740,18 +7892,16 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E62" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
@@ -7768,12 +7918,10 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>85</v>
+        <v>275</v>
       </c>
       <c r="L62" s="2"/>
-      <c r="M62" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M62" s="2"/>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -7799,11 +7947,13 @@
         <v>74</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>74</v>
@@ -7821,7 +7971,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>89</v>
+        <v>274</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7841,23 +7991,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E63" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>74</v>
@@ -7869,12 +8017,10 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>102</v>
+        <v>277</v>
       </c>
       <c r="L63" s="2"/>
-      <c r="M63" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M63" s="2"/>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -7924,13 +8070,13 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>104</v>
+        <v>276</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>74</v>
@@ -7944,23 +8090,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E64" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>74</v>
@@ -7972,12 +8116,10 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>107</v>
+        <v>279</v>
       </c>
       <c r="L64" s="2"/>
-      <c r="M64" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M64" s="2"/>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8027,13 +8169,13 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>109</v>
+        <v>278</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>74</v>
@@ -8047,23 +8189,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E65" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>74</v>
@@ -8075,12 +8215,10 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>112</v>
+        <v>281</v>
       </c>
       <c r="L65" s="2"/>
-      <c r="M65" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M65" s="2"/>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8088,7 +8226,7 @@
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>74</v>
@@ -8130,13 +8268,13 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>115</v>
+        <v>280</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>74</v>
@@ -8150,23 +8288,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E66" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>74</v>
@@ -8178,12 +8314,10 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>102</v>
+        <v>283</v>
       </c>
       <c r="L66" s="2"/>
-      <c r="M66" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M66" s="2"/>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -8233,13 +8367,13 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>119</v>
+        <v>282</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>74</v>
@@ -8253,10 +8387,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8279,12 +8413,10 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>95</v>
+        <v>285</v>
       </c>
       <c r="L67" s="2"/>
-      <c r="M67" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M67" s="2"/>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -8334,7 +8466,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>125</v>
+        <v>284</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8354,10 +8486,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8365,13 +8497,13 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>74</v>
@@ -8380,7 +8512,7 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>85</v>
+        <v>287</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8394,7 +8526,7 @@
         <v>74</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>272</v>
+        <v>74</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>74</v>
@@ -8409,35 +8541,35 @@
         <v>74</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y68" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z68" t="s" s="2">
-        <v>273</v>
+        <v>74</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="AC68" s="2"/>
       <c r="AD68" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>74</v>
@@ -8451,12 +8583,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="C69" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="D69" t="s" s="2">
         <v>74</v>
       </c>
@@ -8477,12 +8611,12 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L69" s="2"/>
-      <c r="M69" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M69" s="2"/>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -8532,13 +8666,13 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>74</v>
@@ -8552,16 +8686,18 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E70" s="2"/>
+      <c r="E70" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
@@ -8578,16 +8714,16 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" t="s" s="2">
-        <v>281</v>
+        <v>86</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
-        <v>282</v>
+        <v>74</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
@@ -8609,13 +8745,11 @@
         <v>74</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>74</v>
@@ -8633,7 +8767,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>283</v>
+        <v>89</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8653,10 +8787,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8667,7 +8801,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>74</v>
@@ -8679,10 +8813,12 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="L71" s="2"/>
-      <c r="M71" s="2"/>
+      <c r="M71" t="s" s="2">
+        <v>92</v>
+      </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -8732,13 +8868,13 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>286</v>
+        <v>93</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>74</v>
@@ -8752,10 +8888,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8778,10 +8914,12 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>289</v>
+        <v>95</v>
       </c>
       <c r="L72" s="2"/>
-      <c r="M72" s="2"/>
+      <c r="M72" t="s" s="2">
+        <v>96</v>
+      </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -8831,7 +8969,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>290</v>
+        <v>97</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8843,7 +8981,7 @@
         <v>74</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>74</v>
@@ -8851,16 +8989,18 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E73" s="2"/>
+      <c r="E73" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
@@ -8877,10 +9017,12 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>293</v>
+        <v>85</v>
       </c>
       <c r="L73" s="2"/>
-      <c r="M73" s="2"/>
+      <c r="M73" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -8906,13 +9048,11 @@
         <v>74</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>74</v>
@@ -8930,7 +9070,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>294</v>
+        <v>89</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8950,16 +9090,18 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E74" s="2"/>
+      <c r="E74" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F74" t="s" s="2">
         <v>80</v>
       </c>
@@ -8976,10 +9118,12 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>297</v>
+        <v>102</v>
       </c>
       <c r="L74" s="2"/>
-      <c r="M74" s="2"/>
+      <c r="M74" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9029,7 +9173,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>298</v>
+        <v>104</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9049,16 +9193,18 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E75" s="2"/>
+      <c r="E75" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="F75" t="s" s="2">
         <v>80</v>
       </c>
@@ -9075,10 +9221,12 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>301</v>
+        <v>107</v>
       </c>
       <c r="L75" s="2"/>
-      <c r="M75" s="2"/>
+      <c r="M75" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -9128,7 +9276,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>302</v>
+        <v>109</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9148,18 +9296,20 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E76" s="2"/>
+      <c r="E76" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="F76" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>75</v>
@@ -9174,10 +9324,12 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>305</v>
+        <v>112</v>
       </c>
       <c r="L76" s="2"/>
-      <c r="M76" s="2"/>
+      <c r="M76" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -9185,7 +9337,7 @@
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>74</v>
@@ -9227,7 +9379,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>306</v>
+        <v>115</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9247,18 +9399,20 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E77" s="2"/>
+      <c r="E77" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F77" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>75</v>
@@ -9273,10 +9427,12 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>309</v>
+        <v>102</v>
       </c>
       <c r="L77" s="2"/>
-      <c r="M77" s="2"/>
+      <c r="M77" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -9326,7 +9482,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>310</v>
+        <v>119</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9346,10 +9502,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9360,7 +9516,7 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>74</v>
@@ -9372,10 +9528,12 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>313</v>
+        <v>95</v>
       </c>
       <c r="L78" s="2"/>
-      <c r="M78" s="2"/>
+      <c r="M78" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -9425,13 +9583,13 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>314</v>
+        <v>125</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>74</v>
@@ -9445,10 +9603,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9456,7 +9614,7 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>75</v>
@@ -9471,7 +9629,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>317</v>
+        <v>85</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9485,7 +9643,7 @@
         <v>74</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>74</v>
+        <v>312</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>74</v>
@@ -9500,13 +9658,11 @@
         <v>74</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>74</v>
+        <v>313</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>74</v>
@@ -9524,10 +9680,10 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>75</v>
@@ -9544,10 +9700,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9570,10 +9726,12 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>321</v>
+        <v>107</v>
       </c>
       <c r="L80" s="2"/>
-      <c r="M80" s="2"/>
+      <c r="M80" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -9623,7 +9781,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9643,10 +9801,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9669,14 +9827,16 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>325</v>
+        <v>107</v>
       </c>
       <c r="L81" s="2"/>
-      <c r="M81" s="2"/>
+      <c r="M81" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
-        <v>74</v>
+        <v>322</v>
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
@@ -9722,7 +9882,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9742,10 +9902,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9768,7 +9928,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>329</v>
+        <v>107</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -9821,7 +9981,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9841,14 +10001,12 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="C83" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
         <v>74</v>
       </c>
@@ -9869,11 +10027,9 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="L83" s="2"/>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -9924,13 +10080,13 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>246</v>
+        <v>330</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>74</v>
@@ -9944,18 +10100,16 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>253</v>
+        <v>332</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E84" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>80</v>
       </c>
@@ -9972,12 +10126,10 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>85</v>
+        <v>333</v>
       </c>
       <c r="L84" s="2"/>
-      <c r="M84" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M84" s="2"/>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -10003,11 +10155,13 @@
         <v>74</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y84" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z84" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>74</v>
@@ -10025,7 +10179,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>89</v>
+        <v>334</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -10045,10 +10199,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>255</v>
+        <v>336</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10059,7 +10213,7 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>74</v>
@@ -10071,12 +10225,10 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>91</v>
+        <v>337</v>
       </c>
       <c r="L85" s="2"/>
-      <c r="M85" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M85" s="2"/>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -10126,13 +10278,13 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>93</v>
+        <v>338</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>74</v>
@@ -10146,10 +10298,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>257</v>
+        <v>340</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10172,12 +10324,10 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>95</v>
+        <v>341</v>
       </c>
       <c r="L86" s="2"/>
-      <c r="M86" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M86" s="2"/>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -10227,7 +10377,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>97</v>
+        <v>342</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10239,7 +10389,7 @@
         <v>74</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>74</v>
@@ -10247,18 +10397,16 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>259</v>
+        <v>344</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E87" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
@@ -10275,12 +10423,10 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>85</v>
+        <v>345</v>
       </c>
       <c r="L87" s="2"/>
-      <c r="M87" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M87" s="2"/>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -10306,11 +10452,13 @@
         <v>74</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y87" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z87" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>74</v>
@@ -10328,7 +10476,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>89</v>
+        <v>346</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10348,18 +10496,16 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>261</v>
+        <v>348</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E88" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
@@ -10376,12 +10522,10 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>102</v>
+        <v>349</v>
       </c>
       <c r="L88" s="2"/>
-      <c r="M88" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M88" s="2"/>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -10431,7 +10575,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>104</v>
+        <v>350</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10451,18 +10595,16 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>263</v>
+        <v>352</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E89" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
@@ -10479,12 +10621,10 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>107</v>
+        <v>353</v>
       </c>
       <c r="L89" s="2"/>
-      <c r="M89" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M89" s="2"/>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -10534,7 +10674,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>109</v>
+        <v>354</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10554,20 +10694,18 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>265</v>
+        <v>356</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E90" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>75</v>
@@ -10582,12 +10720,10 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>112</v>
+        <v>357</v>
       </c>
       <c r="L90" s="2"/>
-      <c r="M90" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M90" s="2"/>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -10595,7 +10731,7 @@
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>74</v>
@@ -10637,7 +10773,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>115</v>
+        <v>358</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10657,20 +10793,18 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>267</v>
+        <v>360</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E91" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>75</v>
@@ -10685,12 +10819,10 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>102</v>
+        <v>361</v>
       </c>
       <c r="L91" s="2"/>
-      <c r="M91" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M91" s="2"/>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -10740,7 +10872,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10760,10 +10892,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>269</v>
+        <v>364</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10774,7 +10906,7 @@
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>74</v>
@@ -10786,12 +10918,10 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>95</v>
+        <v>365</v>
       </c>
       <c r="L92" s="2"/>
-      <c r="M92" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M92" s="2"/>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -10841,13 +10971,13 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>125</v>
+        <v>366</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>74</v>
@@ -10861,10 +10991,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>271</v>
+        <v>368</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10872,7 +11002,7 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>75</v>
@@ -10887,7 +11017,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>85</v>
+        <v>369</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -10901,7 +11031,7 @@
         <v>74</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>343</v>
+        <v>74</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>74</v>
@@ -10916,11 +11046,13 @@
         <v>74</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y93" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z93" t="s" s="2">
-        <v>273</v>
+        <v>74</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>74</v>
@@ -10938,10 +11070,10 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>274</v>
+        <v>370</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>75</v>
@@ -10958,12 +11090,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>344</v>
+        <v>371</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="C94" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="C94" t="s" s="2">
+        <v>372</v>
+      </c>
       <c r="D94" t="s" s="2">
         <v>74</v>
       </c>
@@ -10984,12 +11118,12 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L94" s="2"/>
-      <c r="M94" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M94" s="2"/>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -11039,13 +11173,13 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>74</v>
@@ -11059,16 +11193,18 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E95" s="2"/>
+      <c r="E95" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F95" t="s" s="2">
         <v>80</v>
       </c>
@@ -11085,16 +11221,16 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" t="s" s="2">
-        <v>281</v>
+        <v>86</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
-        <v>282</v>
+        <v>74</v>
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" t="s" s="2">
@@ -11116,13 +11252,11 @@
         <v>74</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y95" s="2"/>
       <c r="Z95" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>74</v>
@@ -11140,7 +11274,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>283</v>
+        <v>89</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11160,10 +11294,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>346</v>
+        <v>374</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11174,7 +11308,7 @@
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>74</v>
@@ -11186,10 +11320,12 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="L96" s="2"/>
-      <c r="M96" s="2"/>
+      <c r="M96" t="s" s="2">
+        <v>92</v>
+      </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -11239,13 +11375,13 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>286</v>
+        <v>93</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>74</v>
@@ -11259,10 +11395,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11285,10 +11421,12 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>289</v>
+        <v>95</v>
       </c>
       <c r="L97" s="2"/>
-      <c r="M97" s="2"/>
+      <c r="M97" t="s" s="2">
+        <v>96</v>
+      </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -11338,7 +11476,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>290</v>
+        <v>97</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11350,7 +11488,7 @@
         <v>74</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>74</v>
@@ -11358,16 +11496,18 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>348</v>
+        <v>376</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E98" s="2"/>
+      <c r="E98" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F98" t="s" s="2">
         <v>80</v>
       </c>
@@ -11384,10 +11524,12 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>293</v>
+        <v>85</v>
       </c>
       <c r="L98" s="2"/>
-      <c r="M98" s="2"/>
+      <c r="M98" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -11413,13 +11555,11 @@
         <v>74</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>74</v>
@@ -11437,7 +11577,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>294</v>
+        <v>89</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11457,16 +11597,18 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E99" s="2"/>
+      <c r="E99" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F99" t="s" s="2">
         <v>80</v>
       </c>
@@ -11483,10 +11625,12 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>297</v>
+        <v>102</v>
       </c>
       <c r="L99" s="2"/>
-      <c r="M99" s="2"/>
+      <c r="M99" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -11536,7 +11680,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>298</v>
+        <v>104</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -11556,16 +11700,18 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E100" s="2"/>
+      <c r="E100" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="F100" t="s" s="2">
         <v>80</v>
       </c>
@@ -11582,10 +11728,12 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>301</v>
+        <v>107</v>
       </c>
       <c r="L100" s="2"/>
-      <c r="M100" s="2"/>
+      <c r="M100" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -11635,7 +11783,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>302</v>
+        <v>109</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -11655,18 +11803,20 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E101" s="2"/>
+      <c r="E101" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="F101" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>75</v>
@@ -11681,10 +11831,12 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>352</v>
+        <v>112</v>
       </c>
       <c r="L101" s="2"/>
-      <c r="M101" s="2"/>
+      <c r="M101" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -11692,7 +11844,7 @@
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>74</v>
@@ -11734,7 +11886,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>306</v>
+        <v>115</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -11754,18 +11906,20 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>353</v>
+        <v>380</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E102" s="2"/>
+      <c r="E102" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F102" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>75</v>
@@ -11780,10 +11934,12 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>309</v>
+        <v>102</v>
       </c>
       <c r="L102" s="2"/>
-      <c r="M102" s="2"/>
+      <c r="M102" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -11833,7 +11989,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>310</v>
+        <v>119</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -11853,10 +12009,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>354</v>
+        <v>381</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11867,7 +12023,7 @@
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>74</v>
@@ -11879,10 +12035,12 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>313</v>
+        <v>95</v>
       </c>
       <c r="L103" s="2"/>
-      <c r="M103" s="2"/>
+      <c r="M103" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -11932,13 +12090,13 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>314</v>
+        <v>125</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>74</v>
@@ -11952,10 +12110,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>355</v>
+        <v>382</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -11963,7 +12121,7 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>75</v>
@@ -11978,7 +12136,7 @@
         <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>317</v>
+        <v>85</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
@@ -11992,7 +12150,7 @@
         <v>74</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>74</v>
+        <v>383</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>74</v>
@@ -12007,13 +12165,11 @@
         <v>74</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>74</v>
+        <v>313</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>74</v>
@@ -12031,10 +12187,10 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>75</v>
@@ -12051,10 +12207,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>356</v>
+        <v>384</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12077,10 +12233,12 @@
         <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>321</v>
+        <v>107</v>
       </c>
       <c r="L105" s="2"/>
-      <c r="M105" s="2"/>
+      <c r="M105" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -12130,7 +12288,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12150,10 +12308,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>357</v>
+        <v>385</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12176,14 +12334,16 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>325</v>
+        <v>107</v>
       </c>
       <c r="L106" s="2"/>
-      <c r="M106" s="2"/>
+      <c r="M106" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
-        <v>74</v>
+        <v>322</v>
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
@@ -12229,7 +12389,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12249,10 +12409,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>358</v>
+        <v>386</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12275,7 +12435,7 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>329</v>
+        <v>107</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
@@ -12328,7 +12488,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12348,10 +12508,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>359</v>
+        <v>328</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12362,7 +12522,7 @@
         <v>80</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>74</v>
@@ -12374,7 +12534,7 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>360</v>
+        <v>329</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -12427,13 +12587,13 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>74</v>
@@ -12447,10 +12607,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>361</v>
+        <v>388</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>361</v>
+        <v>332</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12461,7 +12621,7 @@
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>74</v>
@@ -12473,7 +12633,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>362</v>
+        <v>333</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12526,13 +12686,13 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>361</v>
+        <v>334</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>74</v>
@@ -12546,10 +12706,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>363</v>
+        <v>336</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12560,7 +12720,7 @@
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>74</v>
@@ -12572,7 +12732,7 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>364</v>
+        <v>337</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -12625,13 +12785,13 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>363</v>
+        <v>338</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>74</v>
@@ -12645,10 +12805,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>365</v>
+        <v>390</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>365</v>
+        <v>340</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12659,7 +12819,7 @@
         <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>74</v>
@@ -12671,12 +12831,10 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>366</v>
+        <v>341</v>
       </c>
       <c r="L111" s="2"/>
-      <c r="M111" t="s" s="2">
-        <v>367</v>
-      </c>
+      <c r="M111" s="2"/>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -12726,13 +12884,13 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>365</v>
+        <v>342</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>74</v>
@@ -12746,18 +12904,16 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>368</v>
+        <v>344</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E112" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>80</v>
       </c>
@@ -12774,12 +12930,10 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>85</v>
+        <v>392</v>
       </c>
       <c r="L112" s="2"/>
-      <c r="M112" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M112" s="2"/>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -12805,11 +12959,13 @@
         <v>74</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y112" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z112" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>74</v>
@@ -12827,7 +12983,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>89</v>
+        <v>346</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -12847,10 +13003,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>369</v>
+        <v>393</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -12861,7 +13017,7 @@
         <v>80</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>74</v>
@@ -12873,12 +13029,10 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>91</v>
+        <v>349</v>
       </c>
       <c r="L113" s="2"/>
-      <c r="M113" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M113" s="2"/>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -12928,13 +13082,13 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>93</v>
+        <v>350</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>74</v>
@@ -12948,10 +13102,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>370</v>
+        <v>394</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -12974,12 +13128,10 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>95</v>
+        <v>353</v>
       </c>
       <c r="L114" s="2"/>
-      <c r="M114" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M114" s="2"/>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -13029,7 +13181,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>97</v>
+        <v>354</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13041,7 +13193,7 @@
         <v>74</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>74</v>
@@ -13049,18 +13201,16 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E115" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>80</v>
       </c>
@@ -13077,12 +13227,10 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>85</v>
+        <v>357</v>
       </c>
       <c r="L115" s="2"/>
-      <c r="M115" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M115" s="2"/>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -13108,11 +13256,13 @@
         <v>74</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y115" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z115" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>74</v>
@@ -13130,7 +13280,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>89</v>
+        <v>358</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13150,18 +13300,16 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E116" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>80</v>
       </c>
@@ -13178,12 +13326,10 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>102</v>
+        <v>361</v>
       </c>
       <c r="L116" s="2"/>
-      <c r="M116" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M116" s="2"/>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -13233,7 +13379,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>104</v>
+        <v>362</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -13253,18 +13399,16 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E117" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>80</v>
       </c>
@@ -13281,12 +13425,10 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>107</v>
+        <v>365</v>
       </c>
       <c r="L117" s="2"/>
-      <c r="M117" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M117" s="2"/>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -13336,7 +13478,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>109</v>
+        <v>366</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -13356,20 +13498,18 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>374</v>
+        <v>398</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E118" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
         <v>75</v>
@@ -13384,12 +13524,10 @@
         <v>74</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>112</v>
+        <v>369</v>
       </c>
       <c r="L118" s="2"/>
-      <c r="M118" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M118" s="2"/>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -13397,7 +13535,7 @@
       </c>
       <c r="Q118" s="2"/>
       <c r="R118" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S118" t="s" s="2">
         <v>74</v>
@@ -13439,7 +13577,7 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>115</v>
+        <v>370</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -13459,23 +13597,21 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E119" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>74</v>
@@ -13487,12 +13623,10 @@
         <v>74</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>102</v>
+        <v>400</v>
       </c>
       <c r="L119" s="2"/>
-      <c r="M119" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M119" s="2"/>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -13542,13 +13676,13 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>119</v>
+        <v>399</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>74</v>
@@ -13562,10 +13696,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>376</v>
+        <v>401</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>376</v>
+        <v>401</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13588,12 +13722,10 @@
         <v>74</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>95</v>
+        <v>402</v>
       </c>
       <c r="L120" s="2"/>
-      <c r="M120" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M120" s="2"/>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -13643,7 +13775,7 @@
         <v>74</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>125</v>
+        <v>401</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -13663,10 +13795,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13677,7 +13809,7 @@
         <v>80</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>74</v>
@@ -13689,7 +13821,7 @@
         <v>74</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>85</v>
+        <v>404</v>
       </c>
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
@@ -13700,7 +13832,7 @@
       </c>
       <c r="Q121" s="2"/>
       <c r="R121" t="s" s="2">
-        <v>378</v>
+        <v>74</v>
       </c>
       <c r="S121" t="s" s="2">
         <v>74</v>
@@ -13718,11 +13850,13 @@
         <v>74</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y121" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z121" t="s" s="2">
-        <v>379</v>
+        <v>74</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>74</v>
@@ -13740,13 +13874,13 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>74</v>
@@ -13760,10 +13894,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13771,10 +13905,10 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>74</v>
@@ -13786,10 +13920,12 @@
         <v>74</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="L122" s="2"/>
-      <c r="M122" s="2"/>
+      <c r="M122" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -13839,13 +13975,13 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>74</v>
@@ -13859,21 +13995,23 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E123" s="2"/>
+      <c r="E123" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>74</v>
@@ -13885,10 +14023,12 @@
         <v>74</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>383</v>
+        <v>85</v>
       </c>
       <c r="L123" s="2"/>
-      <c r="M123" s="2"/>
+      <c r="M123" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -13914,13 +14054,11 @@
         <v>74</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y123" s="2"/>
       <c r="Z123" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>74</v>
@@ -13938,26 +14076,1137 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>382</v>
+        <v>89</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G124" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI123" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK123" t="s" s="2">
+      <c r="H124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L124" s="2"/>
+      <c r="M124" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N124" s="2"/>
+      <c r="O124" s="2"/>
+      <c r="P124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L125" s="2"/>
+      <c r="M125" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="O125" s="2"/>
+      <c r="P125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="126" hidden="true">
+      <c r="A126" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L126" s="2"/>
+      <c r="M126" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N126" s="2"/>
+      <c r="O126" s="2"/>
+      <c r="P126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y126" s="2"/>
+      <c r="Z126" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E127" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L127" s="2"/>
+      <c r="M127" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" s="2"/>
+      <c r="P127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E128" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="F128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L128" s="2"/>
+      <c r="M128" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N128" s="2"/>
+      <c r="O128" s="2"/>
+      <c r="P128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E129" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L129" s="2"/>
+      <c r="M129" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N129" s="2"/>
+      <c r="O129" s="2"/>
+      <c r="P129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E130" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L130" s="2"/>
+      <c r="M130" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N130" s="2"/>
+      <c r="O130" s="2"/>
+      <c r="P130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="131" hidden="true">
+      <c r="A131" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L131" s="2"/>
+      <c r="M131" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N131" s="2"/>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="132" hidden="true">
+      <c r="A132" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L132" s="2"/>
+      <c r="M132" s="2"/>
+      <c r="N132" s="2"/>
+      <c r="O132" s="2"/>
+      <c r="P132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y132" s="2"/>
+      <c r="Z132" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="133" hidden="true">
+      <c r="A133" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="L133" s="2"/>
+      <c r="M133" s="2"/>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
+      <c r="P133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="134" hidden="true">
+      <c r="A134" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L134" s="2"/>
+      <c r="M134" s="2"/>
+      <c r="N134" s="2"/>
+      <c r="O134" s="2"/>
+      <c r="P134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK134" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK123">
+  <autoFilter ref="A1:AK134">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13967,7 +15216,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI122">
+  <conditionalFormatting sqref="A2:AI133">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
